--- a/output/pdf_financials_xlsx/ORS.xlsx
+++ b/output/pdf_financials_xlsx/ORS.xlsx
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.056444</v>
+        <v>-0.056444</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.234743</v>
@@ -1418,19 +1418,19 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.19921</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.43226</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-0.774996</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.286794</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.748666</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-1.104842</v>
@@ -1442,10 +1442,10 @@
         <v>-0.442396</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.384252</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.624716</v>
       </c>
     </row>
     <row r="18">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.056444</v>
+        <v>-0.056444</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.234743</v>
@@ -1673,19 +1673,19 @@
         <v>-2.526899</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.099605</v>
+        <v>-0.099605</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.21613</v>
+        <v>-0.21613</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-0.387498</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.643397</v>
+        <v>-0.643397</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.374333</v>
+        <v>-1.374333</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-0.5524210000000001</v>
@@ -1697,10 +1697,10 @@
         <v>-0.221198</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.192126</v>
+        <v>-0.192126</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.812358</v>
+        <v>-0.812358</v>
       </c>
     </row>
     <row r="21">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.056444</v>
+        <v>-0.056444</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.234743</v>
@@ -1856,19 +1856,19 @@
         <v>-2.526899</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.099605</v>
+        <v>-0.099605</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.21613</v>
+        <v>-0.21613</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-0.387498</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.643397</v>
+        <v>-0.643397</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.374333</v>
+        <v>-1.374333</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.5524210000000001</v>
@@ -1880,10 +1880,10 @@
         <v>-0.221198</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.192126</v>
+        <v>-0.192126</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0.812358</v>
+        <v>-0.812358</v>
       </c>
     </row>
     <row r="24">
@@ -2070,16 +2070,16 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>7.204333</v>
+        <v>-7.204333</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>-12.9166</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>21.446567</v>
+        <v>-21.446567</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>34.358325</v>
+        <v>-34.358325</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.056444</v>
+        <v>-0.056444</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.234743</v>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.056444</v>
+        <v>-0.056444</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.234743</v>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -2418,19 +2418,19 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>200</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>200</v>
@@ -2442,10 +2442,10 @@
         <v>200</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -6182,49 +6182,49 @@
         <v>0.00527</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.461134</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.204012</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.380382</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.395934</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.395934</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.395934</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.563202</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.671199</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.423238</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.903628</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.421445</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.421445</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.421445</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.421445</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>4.749261</v>
       </c>
     </row>
     <row r="93">
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.056444</v>
+        <v>-0.056444</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.161468</v>
@@ -10208,7 +10208,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11176,7 +11180,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -14052,7 +14060,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -15810,7 +15822,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -16864,7 +16880,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -38764,34 +38784,34 @@
         </is>
       </c>
       <c r="M290" s="5" t="n">
-        <v>0.099605</v>
+        <v>-0.099605</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>0.21613</v>
+        <v>-0.21613</v>
       </c>
       <c r="O290" s="5" t="n">
-        <v>0.387498</v>
+        <v>-0.387498</v>
       </c>
       <c r="P290" s="5" t="n">
-        <v>0.643397</v>
+        <v>-0.643397</v>
       </c>
       <c r="Q290" s="5" t="n">
-        <v>1.374333</v>
+        <v>-1.374333</v>
       </c>
       <c r="R290" s="5" t="n">
-        <v>0.5524210000000001</v>
+        <v>-0.5524210000000001</v>
       </c>
       <c r="S290" s="5" t="n">
-        <v>0.219457</v>
+        <v>-0.219457</v>
       </c>
       <c r="T290" s="5" t="n">
-        <v>0.221198</v>
+        <v>-0.221198</v>
       </c>
       <c r="U290" s="5" t="n">
-        <v>0.192126</v>
+        <v>-0.192126</v>
       </c>
       <c r="V290" s="5" t="n">
-        <v>0.812358</v>
+        <v>-0.812358</v>
       </c>
     </row>
     <row r="291">
@@ -40161,10 +40181,10 @@
         </is>
       </c>
       <c r="T303" s="5" t="n">
-        <v>0.221198</v>
+        <v>-0.221198</v>
       </c>
       <c r="U303" s="5" t="n">
-        <v>0.192126</v>
+        <v>-0.192126</v>
       </c>
       <c r="V303" t="inlineStr">
         <is>
@@ -46313,10 +46333,10 @@
         </is>
       </c>
       <c r="N362" s="5" t="n">
-        <v>0.21613</v>
+        <v>-0.21613</v>
       </c>
       <c r="O362" s="5" t="n">
-        <v>0.387498</v>
+        <v>-0.387498</v>
       </c>
       <c r="P362" t="inlineStr">
         <is>
@@ -53376,7 +53396,7 @@
         </is>
       </c>
       <c r="E430" s="5" t="n">
-        <v>0.056444</v>
+        <v>-0.056444</v>
       </c>
       <c r="F430" s="5" t="n">
         <v>-0.234743</v>

--- a/output/pdf_financials_xlsx/ORS.xlsx
+++ b/output/pdf_financials_xlsx/ORS.xlsx
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.011658</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.012135</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1101,46 +1101,46 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002069</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009275</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003347</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00059</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000204</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000376</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000373</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000165</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-3.7e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-4e-06</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-4e-06</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-4e-06</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000139</v>
       </c>
     </row>
     <row r="13">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.056444</v>
+        <v>-0.068102</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.234743</v>
+        <v>-0.246878</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.461765</v>
@@ -2126,46 +2126,46 @@
         <v>-0.9137</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.63924</v>
+        <v>-0.637171</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.571151</v>
+        <v>-0.561876</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.378809</v>
+        <v>-0.375462</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.526899</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.099605</v>
+        <v>0.100195</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.21613</v>
+        <v>0.216334</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.387498</v>
+        <v>0.387874</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.643397</v>
+        <v>0.64377</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.374333</v>
+        <v>1.374498</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.5524210000000001</v>
+        <v>0.552458</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.219457</v>
+        <v>0.219461</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.221198</v>
+        <v>0.221202</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.192126</v>
+        <v>0.19213</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.812358</v>
+        <v>0.812497</v>
       </c>
     </row>
     <row r="28">
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.056444</v>
+        <v>-0.068102</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.234743</v>
+        <v>-0.246878</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.460082</v>
@@ -2248,46 +2248,46 @@
         <v>-0.912556</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.638787</v>
+        <v>-0.636718</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.571103</v>
+        <v>-0.561828</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.378699</v>
+        <v>-0.375352</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.52685</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.099718</v>
+        <v>0.100308</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.21613</v>
+        <v>0.216334</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.387498</v>
+        <v>0.387874</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.643397</v>
+        <v>0.64377</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.374333</v>
+        <v>1.374498</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.5524210000000001</v>
+        <v>0.552458</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.219457</v>
+        <v>0.219461</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.221198</v>
+        <v>0.221202</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.192126</v>
+        <v>0.19213</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.812358</v>
+        <v>0.812497</v>
       </c>
     </row>
     <row r="30">
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.117958</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.02935</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.021646</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.190159</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1.037813</v>
@@ -2583,34 +2583,34 @@
         <v>0.011872</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001485</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.106882</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.048349</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.159419</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.069719</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.753796</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.151297</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.00614</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>1.981592</v>
       </c>
     </row>
     <row r="35">
@@ -2681,16 +2681,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.84</v>
+        <v>0.957958</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.02935</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.021646</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.190159</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1.037813</v>
@@ -2705,34 +2705,34 @@
         <v>0.113872</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.000144</v>
+        <v>0.001629</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>9.3e-05</v>
+        <v>0.106975</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>3.3e-05</v>
+        <v>0.048382</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>4.7e-05</v>
+        <v>0.159466</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>3.7e-05</v>
+        <v>0.069756</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>2e-05</v>
+        <v>0.753816</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.151297</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.00614</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>1.981592</v>
       </c>
     </row>
     <row r="37">
@@ -3413,16 +3413,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.254641</v>
+        <v>0.136683</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.057932</v>
+        <v>0.028582</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.100563</v>
+        <v>0.078917</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.440275</v>
+        <v>0.250116</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.277835</v>
@@ -3437,34 +3437,34 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.001485</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.106882</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.053404</v>
+        <v>0.005055</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.217676</v>
+        <v>0.058257</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.082439</v>
+        <v>0.01272</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.818957</v>
+        <v>0.065161</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.157526</v>
+        <v>0.006229</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.009642</v>
+        <v>0.003502</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.0458</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>2.147421</v>
+        <v>0.165829</v>
       </c>
     </row>
     <row r="49">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -38468,7 +38468,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -50742,7 +50742,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" s="5" t="n">

--- a/output/pdf_financials_xlsx/ORS.xlsx
+++ b/output/pdf_financials_xlsx/ORS.xlsx
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.056444</v>
+        <v>0.110049</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.234743</v>
+        <v>-0.196172</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.461765</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.166493</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.038571</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.068102</v>
+        <v>0.09839100000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.246878</v>
+        <v>-0.208307</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.461765</v>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.068102</v>
+        <v>0.09839100000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.246878</v>
+        <v>-0.208307</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.460082</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>151.2898799625621</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-19.66182737597618</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4615,28 +4615,28 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.028152</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.03035</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.029942</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.017225</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.038647</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -4682,22 +4682,22 @@
         <v>0.233785</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.432417</v>
+        <v>0.452417</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.319248</v>
+        <v>0.344248</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.055292</v>
+        <v>0.085642</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.076503</v>
+        <v>0.106445</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.052304</v>
+        <v>0.06952899999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.078679</v>
+        <v>0.117326</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>0.037896</v>
@@ -5109,10 +5109,10 @@
         <v>0.16057</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.045875</v>
+        <v>0.025875</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-0.056444</v>
+        <v>0.056444</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.161468</v>
@@ -6706,22 +6706,22 @@
         <v>-0.002559</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012943</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>0.006434</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>0.007990000000000001</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.000956</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000711</v>
       </c>
       <c r="S101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012428</v>
       </c>
     </row>
     <row r="102">
@@ -7011,22 +7011,22 @@
         <v>-0.09306200000000001</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.171279</v>
+        <v>0.158336</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-0.043968</v>
+        <v>-0.037534</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.102206</v>
+        <v>-0.09421599999999999</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.01758</v>
+        <v>0.018536</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>-0.001963</v>
+        <v>-0.002674</v>
       </c>
       <c r="S106" s="3" t="n">
-        <v>-0.170721</v>
+        <v>-0.183149</v>
       </c>
     </row>
     <row r="107">
@@ -7295,7 +7295,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00032</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.156503</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -7566,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>1.5e-05</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00032</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
         <v>-0.910264</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.167203</v>
+        <v>-0.167523</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.24471</v>
@@ -21520,7 +21520,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -23476,7 +23480,11 @@
           <t>Net proceeds from the private placement 5</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -24610,7 +24618,11 @@
           <t>Proceeds from sale of marketable securities 4</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -25642,7 +25654,11 @@
           <t>Net proceeds from the private placement 6</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -30848,7 +30864,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -32406,7 +32426,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -33348,7 +33372,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -35438,7 +35466,11 @@
           <t>Future income tax</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -36182,7 +36214,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E265" s="5" t="n">
         <v>0.056444</v>
       </c>
@@ -36394,7 +36430,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n">
         <v>-0.166493</v>
       </c>
@@ -53286,7 +53326,11 @@
           <t>Future income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E429" s="5" t="n">
         <v>0.166493</v>
       </c>
